--- a/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,17 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Forms did not show the expected placeholder/categories (missing: ['CIT Returns', 'WHT deduction/Treaty form']).</t>
+          <t>Forms loaded with the placeholder and all 5 categories (CIT Returns, WHT deduction/Treaty form, Administrative, Other Forms, Pillar Two) visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Placeholder and all 5 form categories are visible</t>
+          <t>[PASS] Placeholder and all 5 form categories are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -620,52 +612,114 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction alone did not render the forms table as expected.</t>
+          <t>Selecting Australia alone (no category) rendered the forms table, confirming categories act as an optional filter here, unlike the main Information page.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Forms table renders from jurisdiction alone, no category required</t>
+          <t>[PASS] Forms table renders from jurisdiction alone, no category required</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Forms_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WTA Forms</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>A category checkbox can be toggled off and back on</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Forms.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia / Category: CIT Returns</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Forms, select Australia
+2. Verify 'CIT Returns' starts checked
+3. Click it once and verify it becomes unchecked
+4. Click it again and verify it becomes checked again</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>'CIT Returns' started checked, toggled off on the first click, and toggled back on on the second click - confirming the category filter checkbox is fully interactive.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'CIT Returns' category checkbox is checked by default
+[PASS] 'CIT Returns' becomes unchecked after one click
+[PASS] 'CIT Returns' becomes checked again after a second click</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Forms_04</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Forms</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>'Check All' (already checked by default) toggles every category off</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Forms.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Forms
 2. Verify 'CIT Returns' and 'Pillar Two' start checked
@@ -673,82 +727,142 @@
 4. Verify 'CIT Returns' and 'Pillar Two' both become unchecked</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>The 'Check All' master checkbox and all categories started checked by default; clicking 'Check All' unchecked every category, confirmed via CIT Returns and Pillar Two.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'CIT Returns' and 'Pillar Two' are checked by default
 [PASS] 'CIT Returns' and 'Pillar Two' are unchecked after clicking the already-checked 'Check All'</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Forms_05</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>WTA Forms</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>The Forms page's own Search box accepts free-text input</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Forms.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Search term: company tax return</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Forms
 2. Type 'company tax return' into the Search box
 3. Verify the box holds the typed value</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>The Search box accepted and retained the typed value 'company tax return'.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] Search box holds the typed value</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Forms_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>WTA Forms</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>A row's 'English' download link triggers a real, non-empty file download</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the first row's 'English' download link must trigger a real download with no failure and a non-zero size - not merely be present/visible.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Forms.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Forms
+2. Select Australia
+3. Click the first 'English' download link
+4. Verify a real, non-empty file download completed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the first row's 'English' download link must trigger a real download with no failure and a non-zero size - not merely be present/visible.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>The download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Forms_01</t>
+          <t>Forms_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,142 +522,25 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Forms module loads with the jurisdiction and category panel</t>
+          <t>A category checkbox can be toggled off and back on</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load with the left-panel instruction text and all 5 form categories listed.</t>
+          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Forms.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia / Category: CIT Returns</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Forms
-2. Verify the placeholder text and all 5 categories are visible</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>The page must load with the left-panel instruction text and all 5 form categories listed.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Forms loaded with the placeholder and all 5 categories (CIT Returns, WHT deduction/Treaty form, Administrative, Other Forms, Pillar Two) visible.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder and all 5 form categories are visible</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Forms_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Forms</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting a jurisdiction alone (no category) renders the forms table</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' with no category selected must still render a 'Showing forms of Australia' table, confirming categories here filter rather than gate content.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Forms.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Forms
-2. Check 'Australia' only
-3. Verify the forms table renders without selecting any category</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' with no category selected must still render a 'Showing forms of Australia' table, confirming categories here filter rather than gate content.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia alone (no category) rendered the forms table, confirming categories act as an optional filter here, unlike the main Information page.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Forms table renders from jurisdiction alone, no category required</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Forms_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Forms</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>A category checkbox can be toggled off and back on</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Forms.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia / Category: CIT Returns</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Forms, select Australia
 2. Verify 'CIT Returns' starts checked
@@ -665,61 +548,61 @@
 4. Click it again and verify it becomes checked again</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>'CIT Returns' started checked, toggled off on the first click, and toggled back on on the second click - confirming the category filter checkbox is fully interactive.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'CIT Returns' category checkbox is checked by default
 [PASS] 'CIT Returns' becomes unchecked after one click
 [PASS] 'CIT Returns' becomes checked again after a second click</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Forms_04</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>WTA Forms</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>'Check All' (already checked by default) toggles every category off</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Forms.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Forms
 2. Verify 'CIT Returns' and 'Pillar Two' start checked
@@ -727,142 +610,82 @@
 4. Verify 'CIT Returns' and 'Pillar Two' both become unchecked</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>The 'Check All' master checkbox and all categories started checked by default; clicking 'Check All' unchecked every category, confirmed via CIT Returns and Pillar Two.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'CIT Returns' and 'Pillar Two' are checked by default
 [PASS] 'CIT Returns' and 'Pillar Two' are unchecked after clicking the already-checked 'Check All'</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Forms_05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>WTA Forms</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>The Forms page's own Search box accepts free-text input</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Forms.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Search term: company tax return</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Forms
 2. Type 'company tax return' into the Search box
 3. Verify the box holds the typed value</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>The Search box accepted and retained the typed value 'company tax return'.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] Search box holds the typed value</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Forms_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Forms</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>A row's 'English' download link triggers a real, non-empty file download</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the first row's 'English' download link must trigger a real download with no failure and a non-zero size - not merely be present/visible.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Forms.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Forms
-2. Select Australia
-3. Click the first 'English' download link
-4. Verify a real, non-empty file download completed</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the first row's 'English' download link must trigger a real download with no failure and a non-zero size - not merely be present/visible.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>The download link correctly downloaded 'AU_Form__NAT_0656_06_2025_English_pdf.pdf' (1056759 bytes).</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The 'English' download link produces a real, non-empty file with no failure</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Forms/WTA Forms_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Forms_03</t>
+          <t>Forms_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,47 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>A category checkbox can be toggled off and back on</t>
+          <t>Forms module loads with the jurisdiction and category panel</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
+          <t>The page must load with the left-panel instruction text and all 5 form categories listed.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Forms.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia / Category: CIT Returns</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Forms, select Australia
-2. Verify 'CIT Returns' starts checked
-3. Click it once and verify it becomes unchecked
-4. Click it again and verify it becomes checked again</t>
+          <t>1. Log in and open Forms
+2. Verify the placeholder text and all 5 categories are visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Every form category checkbox (confirmed live) starts CHECKED by default. With Australia selected, clicking 'CIT Returns' once must UNCHECK it, and clicking it again must re-check it.</t>
+          <t>The page must load with the left-panel instruction text and all 5 form categories listed.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>'CIT Returns' started checked, toggled off on the first click, and toggled back on on the second click - confirming the category filter checkbox is fully interactive.</t>
+          <t>Forms loaded with the placeholder and all 5 categories (CIT Returns, WHT deduction/Treaty form, Administrative, Other Forms, Pillar Two) visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'CIT Returns' category checkbox is checked by default
-[PASS] 'CIT Returns' becomes unchecked after one click
-[PASS] 'CIT Returns' becomes checked again after a second click</t>
+          <t>[PASS] Placeholder and all 5 form categories are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -574,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Forms_04</t>
+          <t>Forms_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -584,12 +580,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>'Check All' (already checked by default) toggles every category off</t>
+          <t>Selecting a jurisdiction alone (no category) renders the forms table</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
+          <t>Checking 'Australia' with no category selected must still render a 'Showing forms of Australia' table, confirming categories here filter rather than gate content.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -599,93 +595,32 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Forms
-2. Verify 'CIT Returns' and 'Pillar Two' start checked
-3. Click the 'Check All' master checkbox
-4. Verify 'CIT Returns' and 'Pillar Two' both become unchecked</t>
+2. Check 'Australia' only
+3. Verify the forms table renders without selecting any category</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>The 'checkAllFormCategories' master checkbox and every individual category checkbox start CHECKED by default (confirmed live). Clicking the master checkbox once must therefore UNCHECK every individual category, not check them.</t>
+          <t>Checking 'Australia' with no category selected must still render a 'Showing forms of Australia' table, confirming categories here filter rather than gate content.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The 'Check All' master checkbox and all categories started checked by default; clicking 'Check All' unchecked every category, confirmed via CIT Returns and Pillar Two.</t>
+          <t>Selecting Australia alone (no category) rendered the forms table, confirming categories act as an optional filter here, unlike the main Information page.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'CIT Returns' and 'Pillar Two' are checked by default
-[PASS] 'CIT Returns' and 'Pillar Two' are unchecked after clicking the already-checked 'Check All'</t>
+          <t>[PASS] Forms table renders from jurisdiction alone, no category required</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Forms_05</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Forms</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The Forms page's own Search box accepts free-text input</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Forms.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Search term: company tax return</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Forms
-2. Type 'company tax return' into the Search box
-3. Verify the box holds the typed value</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Typing into the page's 'Search' box (distinct from 'Search countries') must accept the text without error.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The Search box accepted and retained the typed value 'company tax return'.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Search box holds the typed value</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
